--- a/rules/CORE-000093/negative/01/data/unit-test-coreid-CG0114-negative.xlsx
+++ b/rules/CORE-000093/negative/01/data/unit-test-coreid-CG0114-negative.xlsx
@@ -1,58 +1,65 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Validation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ag.xpt" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="cm.xpt" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ec.xpt" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ex.xpt" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="ml.xpt" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="pr.xpt" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="su.xpt" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ag.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cm.xpt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ec.xpt" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ex.xpt" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ml.xpt" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pr.xpt" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="su.xpt" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
-  </numFmts>
-  <fonts count="4">
+  <numFmts count="0"/>
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <i val="1"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -62,13 +69,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFCC"/>
-        <bgColor rgb="00FFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -78,12 +88,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -92,85 +102,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="6"/>
-      </left>
-      <right style="thin">
-        <color theme="6"/>
-      </right>
-      <top style="thin">
-        <color theme="6"/>
-      </top>
-      <bottom style="medium">
-        <color theme="6"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -317,6 +277,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -351,6 +312,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -385,20 +347,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -520,7 +478,46 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -535,12 +532,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
@@ -573,316 +570,316 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>STUDYID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>DOMAIN</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>USUBJID</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>SUSEQ</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>SUTRT</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>SUCAT</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>SUDOSE</t>
         </is>
       </c>
-      <c r="H1" s="16" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>SUDOSTXT</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>SUDOSU</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>SUDOSFRQ</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>SUDOSTOT</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>SUSTDTC</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>SUENDTC</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>SUSTTPT</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>SUSTRTPT</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>SUENTPT</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>SUENRTPT</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Study Identifier</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Domain Abbreviation</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Unique Subject Identifier</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Sequence Number</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Reported Name of Substance</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Category for Substance Use</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Substance Use Consumption</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Substance Use Consumption Text</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>Consumption Units</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Use Frequency Per Interval</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>Total Daily Consumption</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>Start Date/Time of Substance Use</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>End Date/Time of Substance Use</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>Start Reference Time Point</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>Start Relative to Reference Time Point</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>End Reference Time Point</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="Q2" s="5" t="inlineStr">
         <is>
           <t>End Relative to Reference Time Point</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" s="4" t="n">
+      <c r="E4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="K4" s="4" t="n">
+      <c r="H4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="K4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="L4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q4" s="4" t="n">
+      <c r="L4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="5" t="n">
         <v>50</v>
       </c>
     </row>
@@ -914,7 +911,7 @@
       <c r="G5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="14" t="n"/>
+      <c r="H5" s="7" t="str"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>PACK</t>
@@ -925,16 +922,20 @@
           <t>QD</t>
         </is>
       </c>
-      <c r="N5" s="9" t="n">
-        <v>38718</v>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>BEFORE</t>
         </is>
       </c>
-      <c r="P5" s="9" t="n">
-        <v>38718</v>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -957,7 +958,7 @@
       <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>COFFEE</t>
         </is>
@@ -967,21 +968,26 @@
           <t>CAFFEINE</t>
         </is>
       </c>
-      <c r="H6" s="14" t="n"/>
-      <c r="I6" s="6" t="n"/>
+      <c r="G6" s="11" t="str"/>
+      <c r="H6" s="12" t="str"/>
+      <c r="I6" s="10" t="str"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>QD</t>
         </is>
       </c>
-      <c r="K6" s="6" t="n">
+      <c r="K6" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="L6" s="17" t="n">
-        <v>38718</v>
-      </c>
-      <c r="M6" s="17" t="n">
-        <v>38718</v>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -999,12 +1005,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Filename</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
@@ -1105,38 +1111,929 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Error group</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Error level</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Row num</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Error value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ag.xpt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AGTRT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>GRASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ag.xpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AGDOSE</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ag.xpt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AGDOSTXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ag.xpt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AGDOSTOT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ag.xpt</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AGDOSU</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CMTRT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ASPIRIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CMDOSE</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CMDOSTXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CMDOSTOT</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CMDOSU</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ec.xpt</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ECTRT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>BOTTLE A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ec.xpt</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ECDOSE</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ec.xpt</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ECDOSTXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ec.xpt</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ECDOSTOT</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ec.xpt</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ECDOSU</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ex.xpt</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>EXTRT</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>DRUG X</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ex.xpt</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>EXDOSE</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ex.xpt</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>EXDOSTXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ex.xpt</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>EXDOSTOT</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ex.xpt</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>EXDOSU</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ml.xpt</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>MLTRT</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SNACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ml.xpt</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MLDOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ml.xpt</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MLDOSTXT</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ml.xpt</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MLDOSTOT</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ml.xpt</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>MLDOSU</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>pr.xpt</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PRTRT</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>External beam radiation therapy</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>pr.xpt</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PRDOSE</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>pr.xpt</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PRDOSTXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>pr.xpt</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PRDOSTOT</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>pr.xpt</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PRDOSU</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>su.xpt</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SUTRT</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>COFFEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>7</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>su.xpt</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SUDOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>su.xpt</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SUDOSTXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>su.xpt</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>6</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SUDOSTOT</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>7</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>su.xpt</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>6</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>SUDOSU</t>
         </is>
       </c>
     </row>
@@ -1155,244 +2052,244 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>STUDYID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>DOMAIN</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>USUBJID</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>AGSEQ</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>AGTRT</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>AGPRESP</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>AGOCCUR</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>AGDOSE</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>AGDOSTXT</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>AGDOSU</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>AGROUTE</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>VISIT</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>AGENDTC</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Study Identifier</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Domain Abbreviation</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Unique Subject Identifier</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Sequence Number</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Reported Agent Name</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>AG Pre-Specified</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>AG Occurrence</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Dose per Administration</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>Dose Description</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Dose Units</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>Route of Administration</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>Visit Name</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>End Date/Time of Agent</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="5" t="n">
         <v>50</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="M4" s="4" t="n">
+      <c r="E4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="M4" s="5" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1473,7 +2370,7 @@
       <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>GRASS</t>
         </is>
@@ -1488,10 +2385,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="10" t="n">
         <v>250</v>
       </c>
-      <c r="J6" s="6" t="n"/>
+      <c r="I6" s="11" t="str"/>
+      <c r="J6" s="10" t="str"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>RESPIRATORY (INHALATION)</t>
@@ -1639,226 +2537,226 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>STUDYID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>DOMAIN</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>USUBJID</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>CMSEQ</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>CMTRT</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>CMDOSE</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>CMDOSTXT</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>CMDOSU</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>CMDOSFRQ</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>CMDOSTOT</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>CMSTDTC</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>CMENDTC</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Study Identifier</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Domain Abbreviation</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Unique Subject Identifier</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Sequence Number</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Reported Name of Drug, Med, or Therapy</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Dose per Administration</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Dose Description</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Dose Units</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>Dosing Frequency per Interval</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Total Daily Dose</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>Start Date/Time of Medication</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>End Date/Time of Medication</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" s="4" t="n">
+      <c r="E4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="G4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J4" s="4" t="n">
+      <c r="G4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="L4" s="4" t="n">
+      <c r="K4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="L4" s="5" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1899,11 +2797,15 @@
           <t>QD</t>
         </is>
       </c>
-      <c r="K5" s="7" t="n">
-        <v>37987</v>
-      </c>
-      <c r="L5" s="7" t="n">
-        <v>37989</v>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>2004-01-03</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1925,28 +2827,33 @@
       <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>ASPIRIN</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="H6" s="6" t="n"/>
+      <c r="G6" s="11" t="str"/>
+      <c r="H6" s="10" t="str"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>BID</t>
         </is>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="K6" s="7" t="n">
-        <v>37993</v>
-      </c>
-      <c r="L6" s="7" t="n">
-        <v>37993</v>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>2004-01-07</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>2004-01-07</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1986,11 +2893,15 @@
           <t>QD</t>
         </is>
       </c>
-      <c r="K7" s="8" t="n">
-        <v>37995</v>
-      </c>
-      <c r="L7" s="8" t="n">
-        <v>37995</v>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>2004-01-09</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>2004-01-09</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -2030,34 +2941,38 @@
           <t>PRN</t>
         </is>
       </c>
-      <c r="K8" s="7" t="n">
-        <v>37987</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>37995</v>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>2004-01-09</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="K9" s="9" t="n"/>
-      <c r="L9" s="9" t="n"/>
+      <c r="K9" s="7" t="str"/>
+      <c r="L9" s="7" t="str"/>
     </row>
     <row r="10">
-      <c r="K10" s="9" t="n"/>
-      <c r="L10" s="9" t="n"/>
+      <c r="K10" s="7" t="str"/>
+      <c r="L10" s="7" t="str"/>
     </row>
     <row r="11">
-      <c r="K11" s="9" t="n"/>
-      <c r="L11" s="9" t="n"/>
+      <c r="K11" s="7" t="str"/>
+      <c r="L11" s="7" t="str"/>
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="I13" s="10" t="n"/>
-      <c r="J13" s="10" t="n"/>
-      <c r="K13" s="10" t="n"/>
+      <c r="I13" s="7" t="str"/>
+      <c r="J13" s="7" t="str"/>
+      <c r="K13" s="7" t="str"/>
     </row>
     <row r="14">
-      <c r="K14" s="10" t="n"/>
-      <c r="L14" s="10" t="n"/>
+      <c r="K14" s="7" t="str"/>
+      <c r="L14" s="7" t="str"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2070,378 +2985,529 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="n"/>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="n"/>
-      <c r="Q1" s="1" t="n"/>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>STUDYID</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>DOMAIN</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>ECSEQ</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>ECLNKID</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>ECTRT</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>ECPRESP</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>ECOCCUR</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>ECREASOC</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>ECDOSE</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>ECDOSTXT</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>ECDOSU</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>ECDOSFRM</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>ECSTDTC</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>ECENDTC</t>
+        </is>
+      </c>
+      <c r="P1" s="5" t="inlineStr">
+        <is>
+          <t>ECSTDY</t>
+        </is>
+      </c>
+      <c r="Q1" s="5" t="inlineStr">
+        <is>
+          <t>ECENDY</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="n"/>
-      <c r="B2" s="11" t="n"/>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="11" t="n"/>
-      <c r="J2" s="11" t="n"/>
-      <c r="K2" s="11" t="n"/>
-      <c r="L2" s="11" t="n"/>
-      <c r="M2" s="11" t="n"/>
-      <c r="N2" s="11" t="n"/>
-      <c r="O2" s="11" t="n"/>
-      <c r="P2" s="11" t="n"/>
-      <c r="Q2" s="11" t="n"/>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Study Identifier</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Domain Abbreviation</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Unique Subject Identifier</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Sequence Number</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Link ID</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Name of Treatment</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Pre-Specified</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Occurrence</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>Reason for Occur Value</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>Dose</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>Dose Description</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="inlineStr">
+        <is>
+          <t>Dose Units</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>Dose Form</t>
+        </is>
+      </c>
+      <c r="N2" s="8" t="inlineStr">
+        <is>
+          <t>Start Date/Time of Treatment</t>
+        </is>
+      </c>
+      <c r="O2" s="8" t="inlineStr">
+        <is>
+          <t>End Date/Time of Treatment</t>
+        </is>
+      </c>
+      <c r="P2" s="8" t="inlineStr">
+        <is>
+          <t>Study Day of Start of Treatment</t>
+        </is>
+      </c>
+      <c r="Q2" s="8" t="inlineStr">
+        <is>
+          <t>Study Day of End of Treatment</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="n"/>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="11" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="11" t="n"/>
-      <c r="M3" s="11" t="n"/>
-      <c r="N3" s="11" t="n"/>
-      <c r="O3" s="11" t="n"/>
-      <c r="P3" s="11" t="n"/>
-      <c r="Q3" s="11" t="n"/>
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="O3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="P3" s="8" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="Q3" s="8" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>STUDYID</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>DOMAIN</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>USUBJID</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>ECSEQ</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>ECLNKID</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>ECTRT</t>
-        </is>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>ECPRESP</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>ECOCCUR</t>
-        </is>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>ECREASOC</t>
-        </is>
-      </c>
-      <c r="J4" s="12" t="inlineStr">
-        <is>
-          <t>ECDOSE</t>
-        </is>
-      </c>
-      <c r="K4" s="12" t="inlineStr">
-        <is>
-          <t>ECDOSTXT</t>
-        </is>
-      </c>
-      <c r="L4" s="12" t="inlineStr">
-        <is>
-          <t>ECDOSU</t>
-        </is>
-      </c>
-      <c r="M4" s="12" t="inlineStr">
-        <is>
-          <t>ECDOSFRM</t>
-        </is>
-      </c>
-      <c r="N4" s="12" t="inlineStr">
-        <is>
-          <t>ECSTDTC</t>
-        </is>
-      </c>
-      <c r="O4" s="12" t="inlineStr">
-        <is>
-          <t>ECENDTC</t>
-        </is>
-      </c>
-      <c r="P4" s="12" t="inlineStr">
-        <is>
-          <t>ECSTDY</t>
-        </is>
-      </c>
-      <c r="Q4" s="12" t="inlineStr">
-        <is>
-          <t>ECENDY</t>
-        </is>
+      <c r="A4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="P4" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Study Identifier</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Domain Abbreviation</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Unique Subject Identifier</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Sequence Number</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>Link ID</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>Name of Treatment</t>
-        </is>
-      </c>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>Pre-Specified</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>Occurrence</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>Reason for Occur Value</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
-        <is>
-          <t>Dose</t>
-        </is>
-      </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>Dose Description</t>
-        </is>
-      </c>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>Dose Units</t>
-        </is>
-      </c>
-      <c r="M5" s="13" t="inlineStr">
-        <is>
-          <t>Dose Form</t>
-        </is>
-      </c>
-      <c r="N5" s="13" t="inlineStr">
-        <is>
-          <t>Start Date/Time of Treatment</t>
-        </is>
-      </c>
-      <c r="O5" s="13" t="inlineStr">
-        <is>
-          <t>End Date/Time of Treatment</t>
-        </is>
-      </c>
-      <c r="P5" s="13" t="inlineStr">
-        <is>
-          <t>Study Day of Start of Treatment</t>
-        </is>
-      </c>
-      <c r="Q5" s="13" t="inlineStr">
-        <is>
-          <t>Study Day of End of Treatment</t>
-        </is>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ABC1001</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>A2-20110114</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BOTTLE A</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="7" t="str"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>QD</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>2011-01-14</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>2011-01-28</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>Num</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
-        <is>
-          <t>Num</t>
-        </is>
-      </c>
-      <c r="K6" s="13" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="L6" s="13" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="M6" s="13" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="N6" s="13" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="O6" s="13" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="P6" s="13" t="inlineStr">
-        <is>
-          <t>Num</t>
-        </is>
-      </c>
-      <c r="Q6" s="13" t="inlineStr">
-        <is>
-          <t>Num</t>
-        </is>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ABC2001</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>A2-20110114</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>BOTTLE A</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="12" t="str"/>
+      <c r="L6" s="11" t="str"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>QD</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>2011-01-14</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>2011-01-23</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="E7" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="I7" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="J7" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="K7" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="L7" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="N7" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="O7" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="P7" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q7" s="13" t="n">
-        <v>8</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ABC2001</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>A0-20110124</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BOTTLE A</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>PATIENT MISTAKE</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="str"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>QD</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>2011-01-24</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>2011-01-24</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -2457,15 +3523,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ABC1001</t>
+          <t>ABC2001</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>A2-20110114</t>
+          <t>A2-20110125</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2486,7 +3552,7 @@
       <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="K8" s="14" t="n"/>
+      <c r="K8" s="7" t="str"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>TABLET</t>
@@ -2497,211 +3563,20 @@
           <t>QD</t>
         </is>
       </c>
-      <c r="N8" s="9" t="n">
-        <v>40557</v>
-      </c>
-      <c r="O8" s="9" t="n">
-        <v>40571</v>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>2011-01-25</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>2011-01-28</t>
+        </is>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ABC2001</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>A2-20110114</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>BOTTLE A</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" s="14" t="n"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>QD</t>
-        </is>
-      </c>
-      <c r="N9" s="9" t="n">
-        <v>40557</v>
-      </c>
-      <c r="O9" s="9" t="n">
-        <v>40566</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ABC2001</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>A0-20110124</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>BOTTLE A</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>PATIENT MISTAKE</t>
-        </is>
-      </c>
-      <c r="K10" s="14" t="n"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>QD</t>
-        </is>
-      </c>
-      <c r="N10" s="9" t="n">
-        <v>40567</v>
-      </c>
-      <c r="O10" s="9" t="n">
-        <v>40567</v>
-      </c>
-      <c r="P10" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ABC2001</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>A2-20110125</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>BOTTLE A</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" s="14" t="n"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>TABLET</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>QD</t>
-        </is>
-      </c>
-      <c r="N11" s="9" t="n">
-        <v>40568</v>
-      </c>
-      <c r="O11" s="9" t="n">
-        <v>40571</v>
-      </c>
-      <c r="P11" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q11" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2720,298 +3595,298 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>STUDYID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>DOMAIN</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>USUBJID</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>EXSEQ</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>EXLNKID</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>EXTRT</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>EXDOSE</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>EXDOSTXT</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>EXDOSU</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>EXDOSFRM</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>EXDOSFRQ</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>EXROUTE</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>EXSTDTC</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>EXENDTC</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>EXSTDY</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>EXENDY</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Study Identifier</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Domain Abbreviation</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Unique Subject Identifier</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Sequence Number</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Link ID</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Name of Treatment</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Dose</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Dose Description</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>Dose Units</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Dose Form</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>Dosing Frequency per Interval</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>Route of Administration</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>Start Date/Time of Treatment</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>End Date/Time of Treatment</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>Study Day of Start of Treatment</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>Study Day of End of Treatment</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" s="4" t="n">
+      <c r="E4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="O4" s="4" t="n">
+      <c r="H4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="O4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="P4" s="5" t="n">
         <v>8</v>
       </c>
     </row>
@@ -3039,15 +3914,16 @@
           <t>A2-20110114</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>DRUG X</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="10" t="n">
         <v>1000</v>
       </c>
-      <c r="I5" s="6" t="n"/>
+      <c r="H5" s="11" t="str"/>
+      <c r="I5" s="10" t="str"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>TABLET, EXTENDED RELEASE</t>
@@ -3063,11 +3939,15 @@
           <t>ORAL</t>
         </is>
       </c>
-      <c r="M5" s="9" t="n">
-        <v>40557</v>
-      </c>
-      <c r="N5" s="9" t="n">
-        <v>40571</v>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>2011-01-14</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>2011-01-28</t>
+        </is>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -3128,11 +4008,15 @@
           <t>ORAL</t>
         </is>
       </c>
-      <c r="M6" s="9" t="n">
-        <v>40557</v>
-      </c>
-      <c r="N6" s="9" t="n">
-        <v>40566</v>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>2011-01-14</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>2011-01-23</t>
+        </is>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -3193,11 +4077,15 @@
           <t>ORAL</t>
         </is>
       </c>
-      <c r="M7" s="9" t="n">
-        <v>40568</v>
-      </c>
-      <c r="N7" s="9" t="n">
-        <v>40571</v>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>2011-01-25</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>2011-01-28</t>
+        </is>
       </c>
       <c r="O7" t="n">
         <v>12</v>
@@ -3221,316 +4109,316 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>STUDYID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>DOMAIN</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>USUBJID</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>MLSEQ</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>MLTRT</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>MLCAT</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>MLPRESP</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>MLOCCUR</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>MLDOSE</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>MLDOSTXT</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>MLDOSU</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>MLDTC</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>MLSTDTC</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>MLENDTC</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>RELMIDS</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>MIDS</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>MIDSDTC</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Study Identifier</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Domain Abbreviation</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Unique Subject Identifier</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Sequence Number</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Name of Meal</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Category for Meal</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>ML Pre-specified</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>ML Occurrence</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>Dose</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Dose Description</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>Dose Units</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>Date/Time of Collection</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>Start Date/Time of Meal</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>End Date/Time of Meal</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>Temporal Relation to Milestone Instance</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>Disease Milestone Instance Name</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="Q2" s="5" t="inlineStr">
         <is>
           <t>Disease Milestone Instance Date/Time</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I4" s="4" t="n">
+      <c r="E4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q4" s="4" t="n">
+      <c r="J4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="5" t="n">
         <v>50</v>
       </c>
     </row>
@@ -3553,7 +4441,7 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>SNACK</t>
         </is>
@@ -3573,16 +4461,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="I5" s="11" t="str"/>
+      <c r="J5" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="6" t="n"/>
+      <c r="K5" s="10" t="str"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>2015-06-03T14:15</t>
         </is>
       </c>
-      <c r="O5" s="15" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>LAST MEAL PRIOR TO</t>
         </is>
@@ -3617,7 +4506,7 @@
       <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>NUTRITIONAL DRINK</t>
         </is>
@@ -3645,12 +4534,12 @@
           <t>oz</t>
         </is>
       </c>
-      <c r="M6" s="15" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>2015-09-03T08:30</t>
         </is>
       </c>
-      <c r="O6" s="15" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>LAST MEAL PRIOR TO</t>
         </is>
@@ -3660,7 +4549,7 @@
           <t>HYPO2</t>
         </is>
       </c>
-      <c r="Q6" s="15" t="inlineStr">
+      <c r="Q6" s="7" t="inlineStr">
         <is>
           <t>2015-09-03T17:00</t>
         </is>
@@ -3681,226 +4570,226 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>STUDYID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>DOMAIN</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>USUBJID</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>PRSEQ</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>PRTRT</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>PRDOSE</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>PRDOSTXT</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>PRDOSU</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>PRLOC</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>PRLAT</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>PRSTDTC</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>PRENDTC</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Study Identifier</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Domain Abbreviation</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Unique Subject Identifier</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Sequence Number</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Reported Name of Procedure</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Dose</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Dose Description</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Dose Units</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>Location of Procedure</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Laterality</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>Start Date/Time of Procedure</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>End Date/Time of Procedure</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" s="4" t="n">
+      <c r="E4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="G4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="L4" s="4" t="n">
+      <c r="G4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="L4" s="5" t="n">
         <v>50</v>
       </c>
     </row>
@@ -3923,15 +4812,16 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>External beam radiation therapy</t>
         </is>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="H5" s="6" t="n"/>
+      <c r="G5" s="11" t="str"/>
+      <c r="H5" s="10" t="str"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>BREAST</t>
@@ -3942,11 +4832,15 @@
           <t>RIGHT</t>
         </is>
       </c>
-      <c r="K5" s="9" t="n">
-        <v>40695</v>
-      </c>
-      <c r="L5" s="9" t="n">
-        <v>40719</v>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>2011-06-01</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>2011-06-25</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -3986,11 +4880,15 @@
           <t>PROSTATE</t>
         </is>
       </c>
-      <c r="K6" s="9" t="n">
-        <v>40739</v>
-      </c>
-      <c r="L6" s="9" t="n">
-        <v>40739</v>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>2011-07-15</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>2011-07-15</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -4030,11 +4928,15 @@
           <t>BONE</t>
         </is>
       </c>
-      <c r="K7" s="9" t="n">
-        <v>40774</v>
-      </c>
-      <c r="L7" s="9" t="n">
-        <v>40777</v>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>2011-08-19</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>2011-08-22</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/rules/CORE-000093/negative/01/data/unit-test-coreid-CG0114-negative.xlsx
+++ b/rules/CORE-000093/negative/01/data/unit-test-coreid-CG0114-negative.xlsx
@@ -1111,7 +1111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1527,6 +1527,11 @@
           <t>ECDOSU</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2034,6 +2039,272 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>SUDOSU</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>8</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ec.xpt</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>5</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ECTRT</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>BOTTLE A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>8</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ec.xpt</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>5</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ECDOSE</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>8</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ec.xpt</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ECDOSTXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>8</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ec.xpt</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ECDOSTOT</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>8</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ec.xpt</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ECDOSU</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>9</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ec.xpt</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>8</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ECTRT</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>BOTTLE A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>9</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ec.xpt</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ECDOSE</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>9</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ec.xpt</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>8</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ECDOSTXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>9</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ec.xpt</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ECDOSTOT</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>9</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ec.xpt</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>8</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ECDOSU</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
         </is>
       </c>
     </row>
@@ -2964,7 +3235,6 @@
       <c r="K11" s="7" t="str"/>
       <c r="L11" s="7" t="str"/>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="I13" s="7" t="str"/>
       <c r="J13" s="7" t="str"/>
@@ -2985,7 +3255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3046,30 +3316,25 @@
       </c>
       <c r="L1" s="5" t="inlineStr">
         <is>
-          <t>ECDOSU</t>
+          <t>ECDOSFRM</t>
         </is>
       </c>
       <c r="M1" s="5" t="inlineStr">
         <is>
-          <t>ECDOSFRM</t>
+          <t>ECSTDTC</t>
         </is>
       </c>
       <c r="N1" s="5" t="inlineStr">
         <is>
-          <t>ECSTDTC</t>
+          <t>ECENDTC</t>
         </is>
       </c>
       <c r="O1" s="5" t="inlineStr">
         <is>
-          <t>ECENDTC</t>
+          <t>ECSTDY</t>
         </is>
       </c>
       <c r="P1" s="5" t="inlineStr">
-        <is>
-          <t>ECSTDY</t>
-        </is>
-      </c>
-      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>ECENDY</t>
         </is>
@@ -3133,30 +3398,25 @@
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>Dose Units</t>
+          <t>Dose Form</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>Dose Form</t>
+          <t>Start Date/Time of Treatment</t>
         </is>
       </c>
       <c r="N2" s="8" t="inlineStr">
         <is>
-          <t>Start Date/Time of Treatment</t>
+          <t>End Date/Time of Treatment</t>
         </is>
       </c>
       <c r="O2" s="8" t="inlineStr">
         <is>
-          <t>End Date/Time of Treatment</t>
+          <t>Study Day of Start of Treatment</t>
         </is>
       </c>
       <c r="P2" s="8" t="inlineStr">
-        <is>
-          <t>Study Day of Start of Treatment</t>
-        </is>
-      </c>
-      <c r="Q2" s="8" t="inlineStr">
         <is>
           <t>Study Day of End of Treatment</t>
         </is>
@@ -3235,15 +3495,10 @@
       </c>
       <c r="O3" s="8" t="inlineStr">
         <is>
-          <t>Char</t>
+          <t>Num</t>
         </is>
       </c>
       <c r="P3" s="8" t="inlineStr">
-        <is>
-          <t>Num</t>
-        </is>
-      </c>
-      <c r="Q3" s="8" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
@@ -3293,14 +3548,11 @@
         <v>50</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="P4" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="Q4" s="8" t="n">
-        <v>8</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3326,7 +3578,7 @@
           <t>A2-20110114</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>BOTTLE A</t>
         </is>
@@ -3341,34 +3593,29 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="7" t="str"/>
+      <c r="K5" s="12" t="str"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>TABLET</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
           <t>QD</t>
         </is>
       </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>2011-01-14</t>
+        </is>
+      </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>2011-01-14</t>
-        </is>
-      </c>
-      <c r="O5" s="7" t="inlineStr">
-        <is>
           <t>2011-01-28</t>
         </is>
       </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
       <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
         <v>15</v>
       </c>
     </row>
@@ -3415,26 +3662,25 @@
         <v>2</v>
       </c>
       <c r="K6" s="12" t="str"/>
-      <c r="L6" s="11" t="str"/>
-      <c r="M6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>QD</t>
         </is>
       </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>2011-01-14</t>
+        </is>
+      </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>2011-01-14</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
           <t>2011-01-23</t>
         </is>
       </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
       <c r="P6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3485,30 +3731,25 @@
       <c r="K7" s="7" t="str"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>TABLET</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
           <t>QD</t>
         </is>
       </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>2011-01-24</t>
+        </is>
+      </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
           <t>2011-01-24</t>
         </is>
       </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>2011-01-24</t>
-        </is>
+      <c r="O7" t="n">
+        <v>11</v>
       </c>
       <c r="P7" t="n">
         <v>11</v>
       </c>
-      <c r="Q7" t="n">
-        <v>11</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3534,7 +3775,7 @@
           <t>A2-20110125</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>BOTTLE A</t>
         </is>
@@ -3549,34 +3790,29 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="K8" s="7" t="str"/>
+      <c r="K8" s="12" t="str"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>TABLET</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
           <t>QD</t>
         </is>
       </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>2011-01-25</t>
+        </is>
+      </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>2011-01-25</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
           <t>2011-01-28</t>
         </is>
       </c>
+      <c r="O8" t="n">
+        <v>12</v>
+      </c>
       <c r="P8" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q8" t="n">
         <v>15</v>
       </c>
     </row>
